--- a/output/roomself_excel/3694.xlsx
+++ b/output/roomself_excel/3694.xlsx
@@ -498,10 +498,10 @@
         <v>1352</v>
       </c>
       <c r="E3" t="n">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="F3" t="n">
-        <v>194</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">

--- a/output/roomself_excel/3694.xlsx
+++ b/output/roomself_excel/3694.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,197 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_8</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_8</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_8</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_9</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_9</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_9</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_10</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_10</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_10</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_11</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_11</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_11</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_12</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_12</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_12</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_13</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_13</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_13</t>
         </is>
       </c>
     </row>
@@ -475,11 +660,148 @@
       <c r="D2" t="n">
         <v>7656</v>
       </c>
-      <c r="E2" t="n">
-        <v>1243</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>789</v>
+        <v>909</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>314</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>189</v>
+      </c>
+      <c r="M2" t="n">
+        <v>43</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>184</v>
+      </c>
+      <c r="P2" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>73</v>
+      </c>
+      <c r="S2" t="n">
+        <v>42</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>41</v>
+      </c>
+      <c r="V2" t="n">
+        <v>34</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>385</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>348</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>61</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>31</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>323</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +819,53 @@
       <c r="D3" t="n">
         <v>1352</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>177</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>22</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +882,69 @@
       <c r="D4" t="n">
         <v>2196</v>
       </c>
-      <c r="E4" t="n">
-        <v>376</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>242</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="G4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>195</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>354</v>
+      </c>
+      <c r="M4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/3694.xlsx
+++ b/output/roomself_excel/3694.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:CA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,186 @@
           <t>ExtWallWidth_13</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_5</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_5</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_5</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_5</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_6</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_6</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_6</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_6</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_7</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_7</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_7</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_7</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_8</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_8</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_8</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_8</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_9</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_9</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_9</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_9</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +981,150 @@
         <v>323</v>
       </c>
       <c r="AQ2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>421</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>35</v>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>144</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>35</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="BB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>127</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>43</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="BN2" t="n">
+        <v>108</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>42</v>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="BR2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>49</v>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="BV2" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="BZ2" t="n">
+        <v>94</v>
+      </c>
+      <c r="CA2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -866,6 +1190,42 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -945,6 +1305,42 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
